--- a/doc/lol.xlsx
+++ b/doc/lol.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mario\86Box\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A40F3D46-5488-40C4-957E-F1D8F5DC5DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A704FB-B304-4A35-B03A-741461879D12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7BA22BFF-6552-4CB1-8DBC-E95AAB367380}"/>
+    <workbookView xWindow="10515" yWindow="9450" windowWidth="9450" windowHeight="6840" xr2:uid="{7BA22BFF-6552-4CB1-8DBC-E95AAB367380}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>86box bringup</t>
   </si>
@@ -56,6 +55,9 @@
   </si>
   <si>
     <t>Remove 8080, scat and neat</t>
+  </si>
+  <si>
+    <t>Remove old dynarec</t>
   </si>
 </sst>
 </file>
@@ -408,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{700DA3A2-FED4-4A1F-B84E-02E39718B69D}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.140625" bestFit="1" customWidth="1"/>
@@ -505,6 +507,17 @@
         <v>45530.044444444444</v>
       </c>
     </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9">
+        <v>79146447</v>
+      </c>
+      <c r="C9" s="1">
+        <v>45540.959027777775</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
